--- a/el_salleh_final.xlsx
+++ b/el_salleh_final.xlsx
@@ -3935,12 +3935,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>6219831285010</t>
+          <t>6219831265012</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>SP892225</t>
+          <t>SP711140</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -10056,12 +10056,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6219831285010</t>
+          <t>6219831265012</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SP892225</t>
+          <t>SP711140</t>
         </is>
       </c>
       <c r="K44" t="n">
